--- a/evaluation/experiment.xlsx
+++ b/evaluation/experiment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT\THI\PAPER\project\neurosymbolic-legal-reasoner\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB38AF2A-5A8A-44C0-B6B9-23B6ED9F90BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387C9493-C70C-4988-A587-0044F403BB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -6409,11 +6409,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6622,73 +6629,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6704,22 +6711,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7041,7 +7051,7 @@
       <c r="K2" s="28" t="s">
         <v>819</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="35" t="s">
         <v>504</v>
       </c>
       <c r="M2" s="32">
@@ -35726,5 +35736,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>